--- a/artfynd/A 23083-2024 artfynd.xlsx
+++ b/artfynd/A 23083-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118743258</v>
       </c>
       <c r="B2" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 23083-2024 artfynd.xlsx
+++ b/artfynd/A 23083-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>121344585</v>
       </c>
       <c r="B3" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 23083-2024 artfynd.xlsx
+++ b/artfynd/A 23083-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>121344585</v>
       </c>
       <c r="B3" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 23083-2024 artfynd.xlsx
+++ b/artfynd/A 23083-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>121344585</v>
       </c>
       <c r="B3" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 23083-2024 artfynd.xlsx
+++ b/artfynd/A 23083-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>121344585</v>
       </c>
       <c r="B3" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 23083-2024 artfynd.xlsx
+++ b/artfynd/A 23083-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>121344585</v>
       </c>
       <c r="B3" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 23083-2024 artfynd.xlsx
+++ b/artfynd/A 23083-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>121344585</v>
       </c>
       <c r="B3" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 23083-2024 artfynd.xlsx
+++ b/artfynd/A 23083-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>121344585</v>
       </c>
       <c r="B3" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 23083-2024 artfynd.xlsx
+++ b/artfynd/A 23083-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -904,6 +904,228 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123452611</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98370</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Skogsbergstjärnet, Skogsbergstjärnet, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>388095</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6611332</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123452703</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98370</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skogsbergstjärnet, Skogsbergstjärnet, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>388092</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6611327</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23083-2024 artfynd.xlsx
+++ b/artfynd/A 23083-2024 artfynd.xlsx
@@ -909,7 +909,7 @@
         <v>123452611</v>
       </c>
       <c r="B4" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>123452703</v>
       </c>
       <c r="B5" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 23083-2024 artfynd.xlsx
+++ b/artfynd/A 23083-2024 artfynd.xlsx
@@ -906,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123452611</v>
+        <v>123452703</v>
       </c>
       <c r="B4" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -955,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>388095</v>
+        <v>388092</v>
       </c>
       <c r="R4" t="n">
-        <v>6611332</v>
+        <v>6611327</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123452703</v>
+        <v>123452611</v>
       </c>
       <c r="B5" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>388092</v>
+        <v>388095</v>
       </c>
       <c r="R5" t="n">
-        <v>6611327</v>
+        <v>6611332</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 23083-2024 artfynd.xlsx
+++ b/artfynd/A 23083-2024 artfynd.xlsx
@@ -906,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123452703</v>
+        <v>123452611</v>
       </c>
       <c r="B4" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -955,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>388092</v>
+        <v>388095</v>
       </c>
       <c r="R4" t="n">
-        <v>6611327</v>
+        <v>6611332</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123452611</v>
+        <v>123452703</v>
       </c>
       <c r="B5" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>388095</v>
+        <v>388092</v>
       </c>
       <c r="R5" t="n">
-        <v>6611332</v>
+        <v>6611327</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 23083-2024 artfynd.xlsx
+++ b/artfynd/A 23083-2024 artfynd.xlsx
@@ -906,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123452611</v>
+        <v>123452703</v>
       </c>
       <c r="B4" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -955,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>388095</v>
+        <v>388092</v>
       </c>
       <c r="R4" t="n">
-        <v>6611332</v>
+        <v>6611327</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123452703</v>
+        <v>123452611</v>
       </c>
       <c r="B5" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>388092</v>
+        <v>388095</v>
       </c>
       <c r="R5" t="n">
-        <v>6611327</v>
+        <v>6611332</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 23083-2024 artfynd.xlsx
+++ b/artfynd/A 23083-2024 artfynd.xlsx
@@ -909,7 +909,7 @@
         <v>123452703</v>
       </c>
       <c r="B4" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>123452611</v>
       </c>
       <c r="B5" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 23083-2024 artfynd.xlsx
+++ b/artfynd/A 23083-2024 artfynd.xlsx
@@ -906,7 +906,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123452703</v>
+        <v>123452611</v>
       </c>
       <c r="B4" t="n">
         <v>98079</v>
@@ -941,7 +941,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -955,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>388092</v>
+        <v>388095</v>
       </c>
       <c r="R4" t="n">
-        <v>6611327</v>
+        <v>6611332</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,7 +1017,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123452611</v>
+        <v>123452703</v>
       </c>
       <c r="B5" t="n">
         <v>98079</v>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>388095</v>
+        <v>388092</v>
       </c>
       <c r="R5" t="n">
-        <v>6611332</v>
+        <v>6611327</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 23083-2024 artfynd.xlsx
+++ b/artfynd/A 23083-2024 artfynd.xlsx
@@ -906,7 +906,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123452611</v>
+        <v>123452703</v>
       </c>
       <c r="B4" t="n">
         <v>98079</v>
@@ -941,7 +941,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -955,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>388095</v>
+        <v>388092</v>
       </c>
       <c r="R4" t="n">
-        <v>6611332</v>
+        <v>6611327</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,7 +1017,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123452703</v>
+        <v>123452611</v>
       </c>
       <c r="B5" t="n">
         <v>98079</v>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>388092</v>
+        <v>388095</v>
       </c>
       <c r="R5" t="n">
-        <v>6611327</v>
+        <v>6611332</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 23083-2024 artfynd.xlsx
+++ b/artfynd/A 23083-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1126,6 +1126,438 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125684882</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>388051</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6611343</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125684867</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>388027</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6611349</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125684883</v>
+      </c>
+      <c r="B8" t="n">
+        <v>90712</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5754</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gultoppig fingersvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ramaria testaceoflava</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>388040</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6611346</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125684778</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>388059</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6611355</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23083-2024 artfynd.xlsx
+++ b/artfynd/A 23083-2024 artfynd.xlsx
@@ -1128,15 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125684882</v>
+        <v>125684778</v>
       </c>
       <c r="B6" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1161,17 +1156,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stockbergen, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>388051</v>
+        <v>388059</v>
       </c>
       <c r="R6" t="n">
-        <v>6611343</v>
+        <v>6611355</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1198,12 +1197,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1235,15 +1234,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125684867</v>
+        <v>125684882</v>
       </c>
       <c r="B7" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>388027</v>
+        <v>388051</v>
       </c>
       <c r="R7" t="n">
-        <v>6611349</v>
+        <v>6611343</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1305,12 +1299,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1342,37 +1336,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125684883</v>
+        <v>125684867</v>
       </c>
       <c r="B8" t="n">
-        <v>90712</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5754</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>388040</v>
+        <v>388027</v>
       </c>
       <c r="R8" t="n">
-        <v>6611346</v>
+        <v>6611349</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1412,12 +1401,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1449,54 +1438,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125684778</v>
+        <v>125684883</v>
       </c>
       <c r="B9" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90766</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5754</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stockbergen, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>388059</v>
+        <v>388040</v>
       </c>
       <c r="R9" t="n">
-        <v>6611355</v>
+        <v>6611346</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1523,12 +1503,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">

--- a/artfynd/A 23083-2024 artfynd.xlsx
+++ b/artfynd/A 23083-2024 artfynd.xlsx
@@ -1131,7 +1131,7 @@
         <v>125684778</v>
       </c>
       <c r="B6" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>125684882</v>
       </c>
       <c r="B7" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,32 +1336,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125684867</v>
+        <v>125684883</v>
       </c>
       <c r="B8" t="n">
-        <v>98324</v>
+        <v>90773</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5754</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>388027</v>
+        <v>388040</v>
       </c>
       <c r="R8" t="n">
-        <v>6611349</v>
+        <v>6611346</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1401,12 +1401,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1438,32 +1438,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125684883</v>
+        <v>125684867</v>
       </c>
       <c r="B9" t="n">
-        <v>90766</v>
+        <v>98331</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5754</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1473,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>388040</v>
+        <v>388027</v>
       </c>
       <c r="R9" t="n">
-        <v>6611346</v>
+        <v>6611349</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1503,12 +1503,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">

--- a/artfynd/A 23083-2024 artfynd.xlsx
+++ b/artfynd/A 23083-2024 artfynd.xlsx
@@ -1131,7 +1131,7 @@
         <v>125684778</v>
       </c>
       <c r="B6" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>125684882</v>
       </c>
       <c r="B7" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>125684883</v>
       </c>
       <c r="B8" t="n">
-        <v>90773</v>
+        <v>90774</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>125684867</v>
       </c>
       <c r="B9" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 23083-2024 artfynd.xlsx
+++ b/artfynd/A 23083-2024 artfynd.xlsx
@@ -1336,32 +1336,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125684883</v>
+        <v>125684867</v>
       </c>
       <c r="B8" t="n">
-        <v>90774</v>
+        <v>98334</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5754</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>388040</v>
+        <v>388027</v>
       </c>
       <c r="R8" t="n">
-        <v>6611346</v>
+        <v>6611349</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1401,12 +1401,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1438,32 +1438,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125684867</v>
+        <v>125684883</v>
       </c>
       <c r="B9" t="n">
-        <v>98334</v>
+        <v>90774</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5754</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1473,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>388027</v>
+        <v>388040</v>
       </c>
       <c r="R9" t="n">
-        <v>6611349</v>
+        <v>6611346</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1503,12 +1503,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">

--- a/artfynd/A 23083-2024 artfynd.xlsx
+++ b/artfynd/A 23083-2024 artfynd.xlsx
@@ -1131,7 +1131,7 @@
         <v>125684778</v>
       </c>
       <c r="B6" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>125684882</v>
       </c>
       <c r="B7" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,32 +1336,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125684867</v>
+        <v>125684883</v>
       </c>
       <c r="B8" t="n">
-        <v>98334</v>
+        <v>90778</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5754</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>388027</v>
+        <v>388040</v>
       </c>
       <c r="R8" t="n">
-        <v>6611349</v>
+        <v>6611346</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1401,12 +1401,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1438,32 +1438,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125684883</v>
+        <v>125684867</v>
       </c>
       <c r="B9" t="n">
-        <v>90774</v>
+        <v>98338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5754</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1473,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>388040</v>
+        <v>388027</v>
       </c>
       <c r="R9" t="n">
-        <v>6611346</v>
+        <v>6611349</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1503,12 +1503,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">

--- a/artfynd/A 23083-2024 artfynd.xlsx
+++ b/artfynd/A 23083-2024 artfynd.xlsx
@@ -1131,7 +1131,7 @@
         <v>125684778</v>
       </c>
       <c r="B6" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>125684882</v>
       </c>
       <c r="B7" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>125684867</v>
       </c>
       <c r="B9" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 23083-2024 artfynd.xlsx
+++ b/artfynd/A 23083-2024 artfynd.xlsx
@@ -1336,32 +1336,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125684883</v>
+        <v>125684867</v>
       </c>
       <c r="B8" t="n">
-        <v>90778</v>
+        <v>98339</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5754</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>388040</v>
+        <v>388027</v>
       </c>
       <c r="R8" t="n">
-        <v>6611346</v>
+        <v>6611349</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1401,12 +1401,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1438,32 +1438,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125684867</v>
+        <v>125684883</v>
       </c>
       <c r="B9" t="n">
-        <v>98339</v>
+        <v>90778</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5754</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1473,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>388027</v>
+        <v>388040</v>
       </c>
       <c r="R9" t="n">
-        <v>6611349</v>
+        <v>6611346</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1503,12 +1503,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">

--- a/artfynd/A 23083-2024 artfynd.xlsx
+++ b/artfynd/A 23083-2024 artfynd.xlsx
@@ -1131,7 +1131,7 @@
         <v>125684778</v>
       </c>
       <c r="B6" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>125684882</v>
       </c>
       <c r="B7" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>125684867</v>
       </c>
       <c r="B8" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>125684883</v>
       </c>
       <c r="B9" t="n">
-        <v>90778</v>
+        <v>90780</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 23083-2024 artfynd.xlsx
+++ b/artfynd/A 23083-2024 artfynd.xlsx
@@ -1131,7 +1131,7 @@
         <v>125684778</v>
       </c>
       <c r="B6" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>125684882</v>
       </c>
       <c r="B7" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,32 +1336,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125684867</v>
+        <v>125684883</v>
       </c>
       <c r="B8" t="n">
-        <v>98341</v>
+        <v>90782</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5754</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>388027</v>
+        <v>388040</v>
       </c>
       <c r="R8" t="n">
-        <v>6611349</v>
+        <v>6611346</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1401,12 +1401,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1438,32 +1438,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125684883</v>
+        <v>125684867</v>
       </c>
       <c r="B9" t="n">
-        <v>90780</v>
+        <v>98343</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5754</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1473,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>388040</v>
+        <v>388027</v>
       </c>
       <c r="R9" t="n">
-        <v>6611346</v>
+        <v>6611349</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1503,12 +1503,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">

--- a/artfynd/A 23083-2024 artfynd.xlsx
+++ b/artfynd/A 23083-2024 artfynd.xlsx
@@ -1131,7 +1131,7 @@
         <v>125684778</v>
       </c>
       <c r="B6" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>125684882</v>
       </c>
       <c r="B7" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,32 +1336,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125684883</v>
+        <v>125684867</v>
       </c>
       <c r="B8" t="n">
-        <v>90782</v>
+        <v>98345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5754</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>388040</v>
+        <v>388027</v>
       </c>
       <c r="R8" t="n">
-        <v>6611346</v>
+        <v>6611349</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1401,12 +1401,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1438,32 +1438,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125684867</v>
+        <v>125684883</v>
       </c>
       <c r="B9" t="n">
-        <v>98343</v>
+        <v>90784</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5754</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1473,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>388027</v>
+        <v>388040</v>
       </c>
       <c r="R9" t="n">
-        <v>6611349</v>
+        <v>6611346</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1503,12 +1503,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">

--- a/artfynd/A 23083-2024 artfynd.xlsx
+++ b/artfynd/A 23083-2024 artfynd.xlsx
@@ -1131,7 +1131,7 @@
         <v>125684778</v>
       </c>
       <c r="B6" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>125684882</v>
       </c>
       <c r="B7" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,32 +1336,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125684867</v>
+        <v>125684883</v>
       </c>
       <c r="B8" t="n">
-        <v>98345</v>
+        <v>90788</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5754</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>388027</v>
+        <v>388040</v>
       </c>
       <c r="R8" t="n">
-        <v>6611349</v>
+        <v>6611346</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1401,12 +1401,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1438,32 +1438,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125684883</v>
+        <v>125684867</v>
       </c>
       <c r="B9" t="n">
-        <v>90784</v>
+        <v>98349</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5754</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1473,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>388040</v>
+        <v>388027</v>
       </c>
       <c r="R9" t="n">
-        <v>6611346</v>
+        <v>6611349</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1503,12 +1503,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">

--- a/artfynd/A 23083-2024 artfynd.xlsx
+++ b/artfynd/A 23083-2024 artfynd.xlsx
@@ -1131,7 +1131,7 @@
         <v>125684778</v>
       </c>
       <c r="B6" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>125684882</v>
       </c>
       <c r="B7" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>125684867</v>
       </c>
       <c r="B9" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 23083-2024 artfynd.xlsx
+++ b/artfynd/A 23083-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118743258</v>
+        <v>125684884</v>
       </c>
       <c r="B2" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skogsbergstjärnet (Skogsbergstjärnet), Vrm</t>
+          <t>Stockbergen, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>388049</v>
+        <v>388053</v>
       </c>
       <c r="R2" t="n">
-        <v>6611350</v>
+        <v>6611214</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,12 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,74 +765,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lina Lejonberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lina Lejonberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121344585</v>
+        <v>125684885</v>
       </c>
       <c r="B3" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skogsbergstjärnet, V om, Vrm</t>
+          <t>Stockbergen, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>388049</v>
+        <v>388053</v>
       </c>
       <c r="R3" t="n">
-        <v>6611351</v>
+        <v>6611214</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,19 +840,19 @@
           <t>Brunskog</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>S-Arv-0848</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,75 +867,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Lina Lejonberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123452703</v>
+        <v>118747510</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5754</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skogsbergstjärnet, Skogsbergstjärnet, Vrm</t>
+          <t>Kusdrågen, Kusdrågen, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>388092</v>
+        <v>388048</v>
       </c>
       <c r="R4" t="n">
-        <v>6611327</v>
+        <v>6611214</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,12 +944,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,74 +964,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123452611</v>
+        <v>125684883</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5754</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skogsbergstjärnet, Skogsbergstjärnet, Vrm</t>
+          <t>Stockbergen, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>388095</v>
+        <v>388040</v>
       </c>
       <c r="R5" t="n">
-        <v>6611332</v>
+        <v>6611346</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,12 +1041,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,22 +1066,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Lina Lejonberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Lina Lejonberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125684778</v>
+        <v>118743258</v>
       </c>
       <c r="B6" t="n">
-        <v>98352</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1158,22 +1108,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stockbergen, Vrm</t>
+          <t>Skogsbergstjärnet, Skogsbergstjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>388059</v>
+        <v>388049</v>
       </c>
       <c r="R6" t="n">
-        <v>6611355</v>
+        <v>6611350</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1197,17 +1152,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Stockbergen</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,22 +1172,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lina Lejonberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lina Lejonberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125684882</v>
+        <v>123452611</v>
       </c>
       <c r="B7" t="n">
-        <v>98352</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,20 +1212,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stockbergen, Vrm</t>
+          <t>Skogsbergstjärnet, Skogsbergstjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>388051</v>
+        <v>388095</v>
       </c>
       <c r="R7" t="n">
-        <v>6611343</v>
+        <v>6611332</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1299,17 +1258,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Stockbergen</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1324,60 +1278,69 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lina Lejonberg</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lina Lejonberg</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125684883</v>
+        <v>123452703</v>
       </c>
       <c r="B8" t="n">
-        <v>90788</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5754</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stockbergen, Vrm</t>
+          <t>Skogsbergstjärnet, Skogsbergstjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>388040</v>
+        <v>388092</v>
       </c>
       <c r="R8" t="n">
-        <v>6611346</v>
+        <v>6611327</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1401,17 +1364,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Stockbergen</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1426,22 +1384,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lina Lejonberg</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lina Lejonberg</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125684867</v>
+        <v>125684778</v>
       </c>
       <c r="B9" t="n">
-        <v>98352</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1466,17 +1424,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stockbergen, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>388027</v>
+        <v>388059</v>
       </c>
       <c r="R9" t="n">
-        <v>6611349</v>
+        <v>6611355</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1503,12 +1465,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1537,6 +1499,210 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>125684867</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>388027</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6611349</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>125684882</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>388051</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6611343</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
